--- a/raw/processedSamples/20250717_r2_GR_USDA-obex_RT-QuIC.xlsx
+++ b/raw/processedSamples/20250717_r2_GR_USDA-obex_RT-QuIC.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\necropsy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rowde002\Documents\Projects\usda-validation\raw\processedSamples\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0433E65A-6106-4488-9FA8-C92F2DA37DE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47687B4A-D87A-40BD-8CFA-07A1D5AE0004}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="105" windowWidth="14610" windowHeight="15585" xr2:uid="{C07FAE0B-72F0-48D4-BB3A-5B0C56B8D655}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{C07FAE0B-72F0-48D4-BB3A-5B0C56B8D655}"/>
   </bookViews>
   <sheets>
     <sheet name="Microplate Cycle 1 (0 h)" sheetId="2" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="626" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="147">
   <si>
     <t>User: USER</t>
   </si>
@@ -447,39 +447,6 @@
     <t>P</t>
   </si>
   <si>
-    <t>O-39_OBEX</t>
-  </si>
-  <si>
-    <t>1904_OBEX</t>
-  </si>
-  <si>
-    <t>1944_OBEX</t>
-  </si>
-  <si>
-    <t>Y-18_OBEX</t>
-  </si>
-  <si>
-    <t>B-167_OBEX</t>
-  </si>
-  <si>
-    <t>B-112_OBEX</t>
-  </si>
-  <si>
-    <t>1942_OBEX</t>
-  </si>
-  <si>
-    <t>B-227_OBEX</t>
-  </si>
-  <si>
-    <t>1901_OBEX</t>
-  </si>
-  <si>
-    <t>1945_OBEX</t>
-  </si>
-  <si>
-    <t>B-166_OBEX</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -742,7 +709,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -799,6 +766,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1190,7 +1160,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="O14" s="19"/>
     </row>
@@ -1232,12 +1202,12 @@
         <v>12</v>
       </c>
       <c r="O15" s="20" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B16" s="11" t="s">
         <v>134</v>
@@ -1279,7 +1249,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>134</v>
@@ -1320,7 +1290,7 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>134</v>
@@ -1361,7 +1331,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>134</v>
@@ -1402,10 +1372,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C20" s="12">
         <v>2265</v>
@@ -1443,10 +1413,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C21" s="12">
         <v>2265</v>
@@ -1484,10 +1454,10 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C22" s="12">
         <v>2265</v>
@@ -1525,10 +1495,10 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B23" s="16" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C23" s="12">
         <v>2265</v>
@@ -1566,7 +1536,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B25" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="O25" s="19"/>
     </row>
@@ -1608,12 +1578,12 @@
         <v>12</v>
       </c>
       <c r="O26" s="20" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B27" s="11">
         <v>1000</v>
@@ -1655,7 +1625,7 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="B28" s="5">
         <v>1000</v>
@@ -1696,7 +1666,7 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="B29" s="5">
         <v>1000</v>
@@ -1737,7 +1707,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B30" s="5">
         <v>1000</v>
@@ -1778,7 +1748,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="B31" s="5">
         <v>1000</v>
@@ -1819,7 +1789,7 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="B32" s="5">
         <v>1000</v>
@@ -1860,7 +1830,7 @@
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B33" s="5">
         <v>1000</v>
@@ -1901,7 +1871,7 @@
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B34" s="16">
         <v>1000</v>
@@ -2618,298 +2588,298 @@
         <v>133</v>
       </c>
     </row>
-    <row r="13" spans="1:98" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+    <row r="13" spans="1:98" x14ac:dyDescent="0.25">
+      <c r="A13" s="22" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="3"/>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="12">
+        <v>2265</v>
+      </c>
+      <c r="E13" s="12">
+        <v>2266</v>
+      </c>
+      <c r="F13" s="12">
+        <v>2267</v>
+      </c>
+      <c r="G13" s="12">
+        <v>2268</v>
+      </c>
+      <c r="H13" s="12">
+        <v>2269</v>
+      </c>
+      <c r="I13" s="12">
+        <v>2270</v>
+      </c>
+      <c r="J13" s="12">
+        <v>2271</v>
+      </c>
+      <c r="K13" s="12">
+        <v>2272</v>
+      </c>
+      <c r="L13" s="12">
+        <v>2273</v>
+      </c>
+      <c r="M13" s="12">
+        <v>1971</v>
+      </c>
+      <c r="N13" s="13">
+        <v>1975</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="P13" s="12">
+        <v>2265</v>
+      </c>
+      <c r="Q13" s="12">
+        <v>2266</v>
+      </c>
+      <c r="R13" s="12">
+        <v>2267</v>
+      </c>
+      <c r="S13" s="12">
+        <v>2268</v>
+      </c>
+      <c r="T13" s="12">
+        <v>2269</v>
+      </c>
+      <c r="U13" s="12">
+        <v>2270</v>
+      </c>
+      <c r="V13" s="12">
+        <v>2271</v>
+      </c>
+      <c r="W13" s="12">
+        <v>2272</v>
+      </c>
+      <c r="X13" s="12">
+        <v>2273</v>
+      </c>
+      <c r="Y13" s="12">
+        <v>1971</v>
+      </c>
+      <c r="Z13" s="13">
+        <v>1975</v>
+      </c>
+      <c r="AA13" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB13" s="12">
+        <v>2265</v>
+      </c>
+      <c r="AC13" s="12">
+        <v>2266</v>
+      </c>
+      <c r="AD13" s="12">
+        <v>2267</v>
+      </c>
+      <c r="AE13" s="12">
+        <v>2268</v>
+      </c>
+      <c r="AF13" s="12">
+        <v>2269</v>
+      </c>
+      <c r="AG13" s="12">
+        <v>2270</v>
+      </c>
+      <c r="AH13" s="12">
+        <v>2271</v>
+      </c>
+      <c r="AI13" s="12">
+        <v>2272</v>
+      </c>
+      <c r="AJ13" s="12">
+        <v>2273</v>
+      </c>
+      <c r="AK13" s="12">
+        <v>1971</v>
+      </c>
+      <c r="AL13" s="13">
+        <v>1975</v>
+      </c>
+      <c r="AM13" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="AN13" s="12">
+        <v>2265</v>
+      </c>
+      <c r="AO13" s="12">
+        <v>2266</v>
+      </c>
+      <c r="AP13" s="12">
+        <v>2267</v>
+      </c>
+      <c r="AQ13" s="12">
+        <v>2268</v>
+      </c>
+      <c r="AR13" s="12">
+        <v>2269</v>
+      </c>
+      <c r="AS13" s="12">
+        <v>2270</v>
+      </c>
+      <c r="AT13" s="12">
+        <v>2271</v>
+      </c>
+      <c r="AU13" s="12">
+        <v>2272</v>
+      </c>
+      <c r="AV13" s="12">
+        <v>2273</v>
+      </c>
+      <c r="AW13" s="12">
+        <v>1971</v>
+      </c>
+      <c r="AX13" s="13">
+        <v>1975</v>
+      </c>
+      <c r="AY13" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="N13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="P13" s="4" t="s">
+      <c r="AZ13" s="12">
+        <v>2265</v>
+      </c>
+      <c r="BA13" s="12">
+        <v>2266</v>
+      </c>
+      <c r="BB13" s="12">
+        <v>2267</v>
+      </c>
+      <c r="BC13" s="12">
+        <v>2268</v>
+      </c>
+      <c r="BD13" s="12">
+        <v>2269</v>
+      </c>
+      <c r="BE13" s="12">
+        <v>2270</v>
+      </c>
+      <c r="BF13" s="12">
+        <v>2271</v>
+      </c>
+      <c r="BG13" s="12">
+        <v>2272</v>
+      </c>
+      <c r="BH13" s="12">
+        <v>2273</v>
+      </c>
+      <c r="BI13" s="12">
+        <v>1971</v>
+      </c>
+      <c r="BJ13" s="13">
+        <v>1975</v>
+      </c>
+      <c r="BK13" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="Q13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="R13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="S13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="T13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="U13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="V13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="W13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="X13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="Y13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="Z13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AA13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AB13" s="4" t="s">
+      <c r="BL13" s="12">
+        <v>2265</v>
+      </c>
+      <c r="BM13" s="12">
+        <v>2266</v>
+      </c>
+      <c r="BN13" s="12">
+        <v>2267</v>
+      </c>
+      <c r="BO13" s="12">
+        <v>2268</v>
+      </c>
+      <c r="BP13" s="12">
+        <v>2269</v>
+      </c>
+      <c r="BQ13" s="12">
+        <v>2270</v>
+      </c>
+      <c r="BR13" s="12">
+        <v>2271</v>
+      </c>
+      <c r="BS13" s="12">
+        <v>2272</v>
+      </c>
+      <c r="BT13" s="12">
+        <v>2273</v>
+      </c>
+      <c r="BU13" s="12">
+        <v>1971</v>
+      </c>
+      <c r="BV13" s="13">
+        <v>1975</v>
+      </c>
+      <c r="BW13" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="AC13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AD13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="AE13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="AG13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AH13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AJ13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AK13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="AL13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AM13" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="AN13" s="4" t="s">
+      <c r="BX13" s="12">
+        <v>2265</v>
+      </c>
+      <c r="BY13" s="12">
+        <v>2266</v>
+      </c>
+      <c r="BZ13" s="12">
+        <v>2267</v>
+      </c>
+      <c r="CA13" s="12">
+        <v>2268</v>
+      </c>
+      <c r="CB13" s="12">
+        <v>2269</v>
+      </c>
+      <c r="CC13" s="12">
+        <v>2270</v>
+      </c>
+      <c r="CD13" s="12">
+        <v>2271</v>
+      </c>
+      <c r="CE13" s="12">
+        <v>2272</v>
+      </c>
+      <c r="CF13" s="12">
+        <v>2273</v>
+      </c>
+      <c r="CG13" s="12">
+        <v>1971</v>
+      </c>
+      <c r="CH13" s="13">
+        <v>1975</v>
+      </c>
+      <c r="CI13" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="AO13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="AP13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="AQ13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="AR13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="AS13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AT13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AU13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AV13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AW13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="AX13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AY13" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="AZ13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="BB13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="BC13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="BD13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="BE13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BF13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="BG13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="BH13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="BI13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="BJ13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BK13" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="BL13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="BM13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="BO13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="BP13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="BQ13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="BR13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="BS13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="BT13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="BU13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="BV13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="BW13" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="BX13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="BY13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="BZ13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="CA13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="CB13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="CC13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="CD13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="CE13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="CF13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="CG13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="CH13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="CI13" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="CJ13" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="CK13" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="CL13" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="CM13" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="CN13" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="CO13" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="CP13" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="CQ13" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="CR13" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="CS13" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="CT13" s="5" t="s">
-        <v>145</v>
+      <c r="CJ13" s="12">
+        <v>2265</v>
+      </c>
+      <c r="CK13" s="12">
+        <v>2266</v>
+      </c>
+      <c r="CL13" s="12">
+        <v>2267</v>
+      </c>
+      <c r="CM13" s="12">
+        <v>2268</v>
+      </c>
+      <c r="CN13" s="12">
+        <v>2269</v>
+      </c>
+      <c r="CO13" s="12">
+        <v>2270</v>
+      </c>
+      <c r="CP13" s="12">
+        <v>2271</v>
+      </c>
+      <c r="CQ13" s="12">
+        <v>2272</v>
+      </c>
+      <c r="CR13" s="12">
+        <v>2273</v>
+      </c>
+      <c r="CS13" s="12">
+        <v>1971</v>
+      </c>
+      <c r="CT13" s="13">
+        <v>1975</v>
       </c>
     </row>
     <row r="14" spans="1:98" ht="30" x14ac:dyDescent="0.25">
